--- a/examples/mascetti/decaf_2024.xlsx
+++ b/examples/mascetti/decaf_2024.xlsx
@@ -659,27 +659,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,75 +701,80 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
+          <t>Azienda</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Paese</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Acquisto</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Vendita</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Val. iniz. orig.</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Val. fin. orig.</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Cambio iniz.</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Cambio fin.</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Val. iniz. EUR</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>Val. fin. EUR</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>Giorni</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>Quota %</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>IVAFE</t>
         </is>
@@ -790,53 +796,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>SPKZ (2024-01-12)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>100</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2024-01-12</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" s="4" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>1800</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1.0942</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="O2" s="4" t="n">
         <v>913.91</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="n">
         <v>1732.6</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>355</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>100</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="S2" s="4" t="n">
         <v>3.36</v>
       </c>
     </row>
@@ -856,53 +867,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>MASCETTI CONTE AG</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>MSCT (2024-01-17)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>200</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2024-01-17</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" s="4" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" s="4" t="n">
         <v>2400</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>2800</v>
       </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="4" t="n">
         <v>2400</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="P3" s="4" t="n">
         <v>2800</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>350</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>100</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>5.36</v>
       </c>
     </row>
@@ -922,53 +938,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TAPPETINO STUZZICATO SPA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TPPC (2024-01-22)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>300</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2024-01-22</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" s="4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" s="4" t="n">
         <v>2400</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>2700</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>2400</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="P4" s="4" t="n">
         <v>2700</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>345</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>100</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>5.09</v>
       </c>
     </row>
@@ -988,57 +1009,62 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>SPKZ (2024-02-14)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>50</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2024-02-14</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1.0713</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1.073</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>560.0700000000001</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="P5" s="4" t="n">
         <v>745.5700000000001</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>132</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>100</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="S5" s="4" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -1058,53 +1084,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SPKZ (2024-02-14)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>50</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2024-02-14</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" s="4" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1.0713</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>560.0700000000001</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>866.3</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>322</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>100</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>1.52</v>
       </c>
     </row>
@@ -1120,53 +1151,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>SPRC (2024-02-17)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>25</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2024-02-17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>1375</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1.0768</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1.1043</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>1114.41</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>1245.13</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>208</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>100</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -1186,53 +1222,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLACSONATO A DESTRA CORP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLCS (2024-02-22)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>100</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2024-02-22</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" s="4" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>2200</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1.0844</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="O8" s="4" t="n">
         <v>1844.34</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>2117.62</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>314</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>100</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>3.63</v>
       </c>
     </row>
@@ -1252,57 +1293,62 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>SPKZ (2024-04-12)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>100</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2024-04-12</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>1400</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>1600</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1.0652</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1.073</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>1314.31</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>1491.15</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>74</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>100</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1322,53 +1368,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>STUZZICAPUOVA LLC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>STZC (2024-04-17)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>50</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2024-04-17</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" s="4" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1.0638</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>705.02</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="n">
         <v>770.05</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>259</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>100</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>1.09</v>
       </c>
     </row>
@@ -1384,53 +1435,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SPRC (2024-05-17)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>275</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1.0844</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1.1043</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>230.54</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="P11" s="4" t="n">
         <v>249.03</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>118</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>100</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -1446,49 +1502,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SPRC (2024-05-17)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>20</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" s="4" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>1040</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1.0844</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>922.17</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>1001.06</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>229</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>1.25</v>
       </c>
     </row>
@@ -1504,49 +1565,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SPRC (2024-08-17)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>25</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2024-08-17</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" s="4" t="n">
-        <v>1300</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M13" t="n">
         <v>1.0994</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>1182.46</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="P13" s="4" t="n">
         <v>1251.32</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>137</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -1562,54 +1628,59 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SPRC (2024-11-17)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>25</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" s="4" t="n">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" s="4" t="n">
         <v>1350</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="L14" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1.0583</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>1275.63</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="n">
         <v>1251.32</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>45</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>100</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>0.31</v>
       </c>
     </row>
     <row r="15">
-      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1620,12 +1691,12 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>TOTALE</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1633,7 +1704,8 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" s="4" t="n">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" s="4" t="n">
         <v>25.27</v>
       </c>
     </row>
@@ -1648,21 +1720,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1678,50 +1751,55 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
+          <t>Azienda</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t>Data acquisto</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Data vendita</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Corrispettivo EUR</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Costo EUR</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>+/- EUR</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Cambio BCE</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Forex</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>P/L broker</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>P/L broker EUR</t>
         </is>
@@ -1740,38 +1818,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>150</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>2236.72</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>1491.15</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>745.5700000000001</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1.073</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <v>745.5700000000001</v>
       </c>
     </row>
@@ -1788,38 +1871,43 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>SPRC (acquired 2024-02-15)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2024-02-15</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>25</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>1245.13</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>1086.66</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>158.47</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1.1043</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <v>158.47</v>
       </c>
     </row>
@@ -1836,38 +1924,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>SPRC (acquired 2024-05-15)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2024-05-15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>249.03</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>226.39</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>22.64</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1.1043</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>22.64</v>
       </c>
     </row>
@@ -1880,40 +1973,45 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2024-02-07</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>50000</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>46240.64</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>46399.41</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>-158.77</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1.0813</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1924,43 +2022,48 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2024-02-07</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1650</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1477.7</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>1531.18</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>-53.48</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1.1166</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1969,12 +2072,13 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>NETTO</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>714.4299999999999</v>
       </c>
     </row>

--- a/examples/mascetti/decaf_2024.xlsx
+++ b/examples/mascetti/decaf_2024.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>714.4299999999999</v>
+        <v>749.83</v>
       </c>
     </row>
     <row r="15">
@@ -1725,7 +1725,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -1973,7 +1973,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
+          <t>Plusvalenza valutaria USD (LIFO per conto)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2022,12 +2022,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
+          <t>Plusvalenza valutaria USD (LIFO per conto)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2042,10 +2042,10 @@
         <v>1477.7</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1531.18</v>
+        <v>1495.78</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-53.48</v>
+        <v>-18.08</v>
       </c>
       <c r="J6" t="n">
         <v>1.1166</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>714.4299999999999</v>
+        <v>749.83</v>
       </c>
     </row>
   </sheetData>

--- a/examples/mascetti/decaf_2024.xlsx
+++ b/examples/mascetti/decaf_2024.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>25.27</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="14">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>749.83</v>
+        <v>735.6900000000001</v>
       </c>
     </row>
     <row r="15">
@@ -822,33 +822,37 @@
           <t>2024-01-12</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
       <c r="K2" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="M2" t="n">
         <v>1.0942</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0389</v>
+        <v>1.073</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>913.91</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>1732.6</v>
+        <v>1491.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>355</v>
+        <v>165</v>
       </c>
       <c r="R2" t="n">
         <v>100</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>3.36</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="3">
@@ -1319,37 +1323,33 @@
           <t>2024-04-12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" s="4" t="n">
         <v>1400</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="M9" t="n">
         <v>1.0652</v>
       </c>
       <c r="N9" t="n">
-        <v>1.073</v>
+        <v>1.0389</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>1314.31</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1491.15</v>
+        <v>1732.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>74</v>
+        <v>264</v>
       </c>
       <c r="R9" t="n">
         <v>100</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -1706,7 +1706,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" s="4" t="n">
-        <v>25.27</v>
+        <v>25.15</v>
       </c>
     </row>
   </sheetData>
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1823,25 +1823,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2236.72</v>
+        <v>1491.15</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1491.15</v>
+        <v>913.58</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>745.5700000000001</v>
+        <v>577.5700000000001</v>
       </c>
       <c r="J2" t="n">
         <v>1.073</v>
@@ -1852,52 +1852,52 @@
         </is>
       </c>
       <c r="L2" s="4" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>745.5700000000001</v>
+        <v>559.1799999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPRC</t>
+          <t>SPKZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>US13579C2467</t>
+          <t>GB0000000100</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SPRC (acquired 2024-02-15)</t>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1245.13</v>
+        <v>745.5700000000001</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1086.66</v>
+        <v>556.95</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>158.47</v>
+        <v>188.62</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1043</v>
+        <v>1.073</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="L3" s="4" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>158.47</v>
+        <v>186.39</v>
       </c>
     </row>
     <row r="4">
@@ -1924,30 +1924,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SPRC (acquired 2024-05-15)</t>
+          <t>SPRC (acquired 2024-02-15)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>249.03</v>
+        <v>1245.13</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>226.39</v>
+        <v>1117.01</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22.64</v>
+        <v>128.12</v>
       </c>
       <c r="J4" t="n">
         <v>1.1043</v>
@@ -1958,59 +1958,63 @@
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>22.64</v>
+        <v>158.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>SPRC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>US13579C2467</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plusvalenza valutaria USD (LIFO per conto)</t>
+          <t>SPRC (acquired 2024-05-15)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50000</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>46240.64</v>
+        <v>249.03</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>46399.41</v>
+        <v>230.8</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-158.77</v>
+        <v>18.23</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0813</v>
+        <v>1.1043</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="6">
@@ -2027,28 +2031,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1650</v>
+        <v>50000</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1477.7</v>
+        <v>46240.64</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1495.78</v>
+        <v>46399.41</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-18.08</v>
+        <v>-158.77</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1166</v>
+        <v>1.0813</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2063,23 +2067,72 @@
       </c>
     </row>
     <row r="7">
-      <c r="I7" s="6" t="n"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EUR.USD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Plusvalenza valutaria USD (LIFO per conto)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1477.7</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1495.78</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>-18.08</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.1166</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>NETTO</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
-        <v>749.83</v>
+      <c r="I9" s="4" t="n">
+        <v>735.6900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/examples/mascetti/decaf_2024.xlsx
+++ b/examples/mascetti/decaf_2024.xlsx
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>158.47</v>
+        <v>113.19</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="L5" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>22.64</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="6">

--- a/examples/mascetti/decaf_2024.xlsx
+++ b/examples/mascetti/decaf_2024.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,10 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,12 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -443,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -648,7 +653,47 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Controllo coerenza RSU (art. 9 c. 4 TUIR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Vest events nell'anno</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Reddito RSU tassato (EUR)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>4727.27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Cross-check: deve essere sottoinsieme del punto 1 CU "Redditi di lavoro dipendente". Differenza = stipendio + bonus.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:D27"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -684,97 +729,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Cod.</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Simbolo</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Paese</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Acquisto</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Vendita</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Val. iniz. orig.</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Val. fin. orig.</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Cambio iniz.</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Cambio fin.</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Val. iniz. EUR</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Val. fin. EUR</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Giorni</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Quota %</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>IVAFE</t>
         </is>
@@ -1680,7 +1725,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="S15" s="6" t="n"/>
+      <c r="S15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1739,67 +1784,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Simbolo</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Data acquisto</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Data vendita</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Corrispettivo EUR</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Costo EUR</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>+/- EUR</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Cambio BCE</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Forex</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>P/L broker</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>P/L broker EUR</t>
         </is>
@@ -2116,7 +2161,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -2159,37 +2204,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Lordo</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Lordo EUR</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Ritenuta</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Ritenuta EUR</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Netto EUR</t>
         </is>
@@ -2331,9 +2376,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -2410,32 +2455,32 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Saldo USD</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Equiv. EUR</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Giorno lavorativo</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Sopra soglia</t>
         </is>
